--- a/mainWidget/mainWidget/src/database/计算模型-枪击试验.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-枪击试验.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22EC2DEE-DA4B-487E-BCA7-282EA923D98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA2E14C-9F85-4A2E-BC68-A8EA636AE145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="1071">
   <si>
     <t>序号</t>
   </si>
@@ -188,1137 +188,3349 @@
   </si>
   <si>
     <t>-464.3395</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-407.717</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>110.3868</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>383.5115</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>292.9054</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-219.8817</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.8697</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-4.3251</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>11.098</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>199.4088</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-119.3268</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.9847</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.028</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>8.8106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>140.606</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-73.0484</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.511</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3.5165</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>5.1963</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>134.2464</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-7.2274</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1981</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0197</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.3167</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>31.6322</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-8.7223</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1316</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2214</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0439</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>18.0694</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-12.229</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1067</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0236</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.776</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>17.7018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-32.6066</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.7688</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.8899</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>21.5986</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>14.4457</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0063</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0039</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0051</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0058</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0034</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3502</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4335</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.5519</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0449</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1537</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0373</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3849</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0167</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0308</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0134</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0093</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0031</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0129</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0038</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0122</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1049</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0057</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2376</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1385</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0042</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0288</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4182</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0078</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0073</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0561</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0271</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0045</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0191</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0046</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0043</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0059</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0443</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0191</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0133</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0058</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0107</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0049</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0064</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0077</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0034</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0056</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0033</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2746</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4042</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.4622</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.8176</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4969</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1872</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0805</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.328</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2875</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1194</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0701</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6855</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2926</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0208</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1723</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0465</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0895</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0948</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0355</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0158</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1922</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0353</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0273</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1204</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0216</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0089</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1167</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1122</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3337</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0444</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.034</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0254</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0582</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0363</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0342</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0193</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0029</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0029</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0095</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0203</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0031</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0157</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3298</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2306</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0138</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2177</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1519</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1631</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0074</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0052</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1309</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0883</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0044</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0079</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0071</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.112</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0505</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0062</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.086</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0127</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0063</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0194</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0169</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0079</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0145</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0221</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0054</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0824</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1436</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.938</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7897</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1817</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0072</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0358</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6625</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2076</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0245</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.558</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1322</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0377</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1053</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0113</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0319</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0591</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0091</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0711</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0055</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0064</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0976</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0082</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0091</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0098</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0167</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0044</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>12.3105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>5.9609</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-5.5476</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1148</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>5.4433</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>5.2484</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2429</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.7202</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1478</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8966</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3949</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.5431</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0503</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.1965</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.045</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4209</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3725</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.4166</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1705</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2898</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0155</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0228</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0295</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0028</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4236</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0457</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0502</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0074</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.285</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7517</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0635</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2728</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0136</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4654</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-8.2997</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0937</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1237</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1069</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.0542</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>70.5917 - 0.0012*B + 0.0000*C + 0.2158*D + 0.0121*E + 0.0019*F + 0.0000*G - 0.2298*H + 0.0220*I + 0.0698*J - 0.2695*K + 1.8961*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>70.5917</t>
+  </si>
+  <si>
+    <t>-0.0012</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>0.2158</t>
+  </si>
+  <si>
+    <t>0.0121</t>
+  </si>
+  <si>
+    <t>0.0019</t>
+  </si>
+  <si>
+    <t>-0.2298</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>0.0698</t>
+  </si>
+  <si>
+    <t>-0.2695</t>
+  </si>
+  <si>
+    <t>1.8961</t>
+  </si>
+  <si>
+    <t>-65.2187 - 0.0005*B + 0.0000*C - 0.2986*D - 0.0216*E - 0.0011*F + 0.0000*G - 0.5415*H + 0.0039*I - 0.0794*J - 0.5261*K + 4.7270*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-65.2187</t>
+  </si>
+  <si>
+    <t>-0.0005</t>
+  </si>
+  <si>
+    <t>-0.2986</t>
+  </si>
+  <si>
+    <t>-0.0216</t>
+  </si>
+  <si>
+    <t>-0.0011</t>
+  </si>
+  <si>
+    <t>-0.5415</t>
+  </si>
+  <si>
+    <t>0.0039</t>
+  </si>
+  <si>
+    <t>-0.0794</t>
+  </si>
+  <si>
+    <t>-0.5261</t>
+  </si>
+  <si>
+    <t>4.727</t>
+  </si>
+  <si>
+    <t>10.0293 - 0.0034*B + 0.0000*C - 0.0236*D - 0.0025*E - 0.0065*F + 0.0000*G + 0.0144*H - 0.0091*I - 0.0245*J - 0.3055*K + 5.9127*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>10.0293</t>
+  </si>
+  <si>
+    <t>-0.0034</t>
+  </si>
+  <si>
+    <t>-0.0236</t>
+  </si>
+  <si>
+    <t>-0.0025</t>
+  </si>
+  <si>
+    <t>-0.0065</t>
+  </si>
+  <si>
+    <t>0.0144</t>
+  </si>
+  <si>
+    <t>-0.0091</t>
+  </si>
+  <si>
+    <t>-0.0245</t>
+  </si>
+  <si>
+    <t>-0.3055</t>
+  </si>
+  <si>
+    <t>5.9127</t>
+  </si>
+  <si>
+    <t>-148.7532 + 0.0005*B + 0.0000*C - 0.1595*D - 0.0015*E - 0.0139*F + 0.0000*G - 0.6677*H + 0.0023*I + 0.0672*J - 0.0951*K - 0.1224*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-148.7532</t>
+  </si>
+  <si>
+    <t>0.0005</t>
+  </si>
+  <si>
+    <t>-0.1595</t>
+  </si>
+  <si>
+    <t>-0.0015</t>
+  </si>
+  <si>
+    <t>-0.0139</t>
+  </si>
+  <si>
+    <t>-0.6677</t>
+  </si>
+  <si>
+    <t>0.0023</t>
+  </si>
+  <si>
+    <t>0.0672</t>
+  </si>
+  <si>
+    <t>-0.0951</t>
+  </si>
+  <si>
+    <t>-0.1224</t>
+  </si>
+  <si>
+    <t>-208.1338 - 0.0022*B + 0.0000*C - 0.0068*D + 0.0073*E + 0.0073*F + 0.0000*G - 0.8418*H + 0.0041*I - 0.0328*J - 0.3260*K + 2.1081*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>-208.1338</t>
+  </si>
+  <si>
+    <t>-0.0022</t>
+  </si>
+  <si>
+    <t>-0.0068</t>
+  </si>
+  <si>
+    <t>0.0073</t>
+  </si>
+  <si>
+    <t>-0.8418</t>
+  </si>
+  <si>
+    <t>0.0041</t>
+  </si>
+  <si>
+    <t>-0.0328</t>
+  </si>
+  <si>
+    <t>-0.326</t>
+  </si>
+  <si>
+    <t>2.1081</t>
+  </si>
+  <si>
+    <t>0.0001</t>
+  </si>
+  <si>
+    <t>131.9133 - 0.0024*B + 0.0000*C + 0.0236*D - 0.0003*E + 0.0131*F + 0.0000*G - 0.3279*H - 0.0032*I - 0.0971*J - 0.4673*K + 2.7240*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>131.9133</t>
+  </si>
+  <si>
+    <t>-0.0024</t>
+  </si>
+  <si>
+    <t>0.0236</t>
+  </si>
+  <si>
+    <t>-0.0003</t>
+  </si>
+  <si>
+    <t>0.0131</t>
+  </si>
+  <si>
+    <t>-0.3279</t>
+  </si>
+  <si>
+    <t>-0.0032</t>
+  </si>
+  <si>
+    <t>-0.0971</t>
+  </si>
+  <si>
+    <t>-0.4673</t>
+  </si>
+  <si>
+    <t>2.724</t>
+  </si>
+  <si>
+    <t>-9.6609 + 0.0008*B + 0.0000*C + 0.1584*D - 0.0104*E + 0.0074*F + 0.0000*G + 0.4797*H - 0.0011*I + 0.1408*J - 0.8548*K + 2.7528*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-9.6609</t>
+  </si>
+  <si>
+    <t>0.0008</t>
+  </si>
+  <si>
+    <t>0.1584</t>
+  </si>
+  <si>
+    <t>-0.0104</t>
+  </si>
+  <si>
+    <t>0.0074</t>
+  </si>
+  <si>
+    <t>0.4797</t>
+  </si>
+  <si>
+    <t>0.1408</t>
+  </si>
+  <si>
+    <t>-0.8548</t>
+  </si>
+  <si>
+    <t>2.7528</t>
+  </si>
+  <si>
+    <t>-41.6925 - 0.0007*B + 0.0000*C - 0.3135*D - 0.0060*E + 0.0074*F + 0.0000*G + 0.4556*H - 0.0080*I - 0.0705*J - 0.2783*K + 3.0395*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>-41.6925</t>
+  </si>
+  <si>
+    <t>-0.0007</t>
+  </si>
+  <si>
+    <t>-0.3135</t>
+  </si>
+  <si>
+    <t>-0.006</t>
+  </si>
+  <si>
+    <t>0.4556</t>
+  </si>
+  <si>
+    <t>-0.008</t>
+  </si>
+  <si>
+    <t>-0.0705</t>
+  </si>
+  <si>
+    <t>-0.2783</t>
+  </si>
+  <si>
+    <t>3.0395</t>
+  </si>
+  <si>
+    <t>-74.2541 + -0.0000*B + 0.0000*C + 0.1052*D + 0.0064*E - 0.0024*F + 0.0000*G - 0.2672*H - 0.0062*I - 0.1289*J - 0.0612*K + 1.0328*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-74.2541</t>
+  </si>
+  <si>
+    <t>-0.0</t>
+  </si>
+  <si>
+    <t>0.1052</t>
+  </si>
+  <si>
+    <t>0.0064</t>
+  </si>
+  <si>
+    <t>-0.2672</t>
+  </si>
+  <si>
+    <t>-0.0062</t>
+  </si>
+  <si>
+    <t>-0.1289</t>
+  </si>
+  <si>
+    <t>-0.0612</t>
+  </si>
+  <si>
+    <t>1.0328</t>
+  </si>
+  <si>
+    <t>-32.6022 - 0.0034*B + 0.0000*C + 0.0012*D - 0.0073*E - 0.0033*F + 0.0000*G - 0.2006*H + 0.0052*I + 0.1694*J - 0.0943*K + 1.0221*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-32.6022</t>
+  </si>
+  <si>
+    <t>0.0012</t>
+  </si>
+  <si>
+    <t>-0.0073</t>
+  </si>
+  <si>
+    <t>-0.0033</t>
+  </si>
+  <si>
+    <t>-0.2006</t>
+  </si>
+  <si>
+    <t>0.0052</t>
+  </si>
+  <si>
+    <t>0.1694</t>
+  </si>
+  <si>
+    <t>-0.0943</t>
+  </si>
+  <si>
+    <t>1.0221</t>
+  </si>
+  <si>
+    <t>-270.2574 - 0.0010*B + 0.0000*C + 0.0978*D + 0.0219*E + 0.0023*F + 0.0000*G - 0.0153*H - 0.0010*I - 0.1026*J + 0.1693*K + 2.5382*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>-270.2574</t>
+  </si>
+  <si>
+    <t>-0.001</t>
+  </si>
+  <si>
+    <t>0.0978</t>
+  </si>
+  <si>
+    <t>0.0219</t>
+  </si>
+  <si>
+    <t>-0.0153</t>
+  </si>
+  <si>
+    <t>-0.1026</t>
+  </si>
+  <si>
+    <t>0.1693</t>
+  </si>
+  <si>
+    <t>2.5382</t>
+  </si>
+  <si>
+    <t>-127.8232 + 0.0015*B + 0.0000*C - 0.1958*D + 0.0024*E + 0.0243*F + 0.0000*G - 0.5326*H - 0.0086*I + 0.0103*J - 0.2788*K - 4.5232*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-127.8232</t>
+  </si>
+  <si>
+    <t>0.0015</t>
+  </si>
+  <si>
+    <t>-0.1958</t>
+  </si>
+  <si>
+    <t>0.0024</t>
+  </si>
+  <si>
+    <t>0.0243</t>
+  </si>
+  <si>
+    <t>-0.5326</t>
+  </si>
+  <si>
+    <t>-0.0086</t>
+  </si>
+  <si>
+    <t>0.0103</t>
+  </si>
+  <si>
+    <t>-0.2788</t>
+  </si>
+  <si>
+    <t>-4.5232</t>
+  </si>
+  <si>
+    <t>-149.4013 - 0.0001*B + 0.0000*C - 0.0990*D + 0.0124*E - 0.0031*F + 0.0000*G - 0.2650*H + 0.0111*I - 0.1082*J - 0.0799*K + 4.2409*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>-149.4013</t>
+  </si>
+  <si>
+    <t>-0.0001</t>
+  </si>
+  <si>
+    <t>-0.099</t>
+  </si>
+  <si>
+    <t>0.0124</t>
+  </si>
+  <si>
+    <t>-0.0031</t>
+  </si>
+  <si>
+    <t>-0.265</t>
+  </si>
+  <si>
+    <t>0.0111</t>
+  </si>
+  <si>
+    <t>-0.1082</t>
+  </si>
+  <si>
+    <t>-0.0799</t>
+  </si>
+  <si>
+    <t>4.2409</t>
+  </si>
+  <si>
+    <t>26.5541 - 0.0005*B + 0.0000*C + 0.2427*D - 0.0166*E - 0.0081*F + 0.0000*G + 0.0729*H + 0.0037*I + 0.0238*J - 0.0475*K - 1.8532*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>26.5541</t>
+  </si>
+  <si>
+    <t>0.2427</t>
+  </si>
+  <si>
+    <t>-0.0166</t>
+  </si>
+  <si>
+    <t>-0.0081</t>
+  </si>
+  <si>
+    <t>0.0729</t>
+  </si>
+  <si>
+    <t>0.0037</t>
+  </si>
+  <si>
+    <t>0.0238</t>
+  </si>
+  <si>
+    <t>-0.0475</t>
+  </si>
+  <si>
+    <t>-1.8532</t>
+  </si>
+  <si>
+    <t>41.8559 - 0.0022*B + 0.0000*C + 0.4605*D + 0.0012*E - 0.0069*F + 0.0000*G + 0.1268*H - 0.0145*I + 0.0716*J + 0.1736*K - 2.2846*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>41.8559</t>
+  </si>
+  <si>
+    <t>0.4605</t>
+  </si>
+  <si>
+    <t>-0.0069</t>
+  </si>
+  <si>
+    <t>0.1268</t>
+  </si>
+  <si>
+    <t>-0.0145</t>
+  </si>
+  <si>
+    <t>0.0716</t>
+  </si>
+  <si>
+    <t>0.1736</t>
+  </si>
+  <si>
+    <t>-2.2846</t>
+  </si>
+  <si>
+    <t>58.7479 + 0.0005*B + 0.0000*C + 0.4667*D - 0.0063*E - 0.0028*F + 0.0000*G - 0.4921*H - 0.0122*I - 0.0054*J - 0.0489*K + 1.0808*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>58.7479</t>
+  </si>
+  <si>
+    <t>0.4667</t>
+  </si>
+  <si>
+    <t>-0.0063</t>
+  </si>
+  <si>
+    <t>-0.0028</t>
+  </si>
+  <si>
+    <t>-0.4921</t>
+  </si>
+  <si>
+    <t>-0.0122</t>
+  </si>
+  <si>
+    <t>-0.0054</t>
+  </si>
+  <si>
+    <t>-0.0489</t>
+  </si>
+  <si>
+    <t>1.0808</t>
+  </si>
+  <si>
+    <t>2.3351 + 0.0016*B + 0.0000*C + 0.0326*D + 0.0246*E + 0.0099*F + 0.0000*G - 0.4792*H - 0.0159*I + 0.0444*J - 0.2026*K + 2.4219*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>2.3351</t>
+  </si>
+  <si>
+    <t>0.0016</t>
+  </si>
+  <si>
+    <t>0.0326</t>
+  </si>
+  <si>
+    <t>0.0246</t>
+  </si>
+  <si>
+    <t>0.0099</t>
+  </si>
+  <si>
+    <t>-0.4792</t>
+  </si>
+  <si>
+    <t>-0.0159</t>
+  </si>
+  <si>
+    <t>0.0444</t>
+  </si>
+  <si>
+    <t>-0.2026</t>
+  </si>
+  <si>
+    <t>2.4219</t>
+  </si>
+  <si>
+    <t>-9.7765 - 0.0024*B + 0.0000*C - 0.2185*D - 0.0083*E + 0.0120*F + 0.0000*G - 0.0503*H - 0.0184*I + 0.0169*J - 0.0369*K - 2.4783*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-9.7765</t>
+  </si>
+  <si>
+    <t>-0.2185</t>
+  </si>
+  <si>
+    <t>-0.0083</t>
+  </si>
+  <si>
+    <t>0.012</t>
+  </si>
+  <si>
+    <t>-0.0503</t>
+  </si>
+  <si>
+    <t>-0.0184</t>
+  </si>
+  <si>
+    <t>0.0169</t>
+  </si>
+  <si>
+    <t>-0.0369</t>
+  </si>
+  <si>
+    <t>-2.4783</t>
+  </si>
+  <si>
+    <t>8.7142 - 0.0029*B + 0.0000*C + 0.1576*D + 0.0021*E + 0.0141*F + 0.0000*G + 0.2858*H - 0.0202*I - 0.0821*J - 0.0016*K + 1.8079*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>8.7142</t>
+  </si>
+  <si>
+    <t>-0.0029</t>
+  </si>
+  <si>
+    <t>0.1576</t>
+  </si>
+  <si>
+    <t>0.0021</t>
+  </si>
+  <si>
+    <t>0.0141</t>
+  </si>
+  <si>
+    <t>0.2858</t>
+  </si>
+  <si>
+    <t>-0.0202</t>
+  </si>
+  <si>
+    <t>-0.0821</t>
+  </si>
+  <si>
+    <t>-0.0016</t>
+  </si>
+  <si>
+    <t>1.8079</t>
+  </si>
+  <si>
+    <t>423.8303 + 0.0001*B + 0.0000*C + 0.3138*D + 0.0062*E + 0.0101*F + 0.0000*G - 0.2623*H + 0.0103*I - 0.0674*J - 0.2062*K - 1.2563*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>423.8303</t>
+  </si>
+  <si>
+    <t>0.3138</t>
+  </si>
+  <si>
+    <t>0.0062</t>
+  </si>
+  <si>
+    <t>0.0101</t>
+  </si>
+  <si>
+    <t>-0.2623</t>
+  </si>
+  <si>
+    <t>-0.0674</t>
+  </si>
+  <si>
+    <t>-0.2062</t>
+  </si>
+  <si>
+    <t>-1.2563</t>
+  </si>
+  <si>
+    <t>327.1218 - 0.0042*B + 0.0000*C + 0.2236*D - 0.0205*E - 0.0002*F + 0.0000*G + 0.2999*H + 0.0004*I - 0.0945*J - 0.3364*K + 2.3164*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>327.1218</t>
+  </si>
+  <si>
+    <t>-0.0042</t>
+  </si>
+  <si>
+    <t>0.2236</t>
+  </si>
+  <si>
+    <t>-0.0205</t>
+  </si>
+  <si>
+    <t>-0.0002</t>
+  </si>
+  <si>
+    <t>0.2999</t>
+  </si>
+  <si>
+    <t>0.0004</t>
+  </si>
+  <si>
+    <t>-0.0945</t>
+  </si>
+  <si>
+    <t>-0.3364</t>
+  </si>
+  <si>
+    <t>2.3164</t>
+  </si>
+  <si>
+    <t>31.0449 - 0.0008*B + 0.0000*C - 0.0452*D + 0.0186*E + 0.0099*F + 0.0000*G - 0.9467*H + 0.0021*I - 0.0575*J + 0.0902*K - 2.1982*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>31.0449</t>
+  </si>
+  <si>
+    <t>-0.0008</t>
+  </si>
+  <si>
+    <t>-0.0452</t>
+  </si>
+  <si>
+    <t>0.0186</t>
+  </si>
+  <si>
+    <t>-0.9467</t>
+  </si>
+  <si>
+    <t>-0.0575</t>
+  </si>
+  <si>
+    <t>0.0902</t>
+  </si>
+  <si>
+    <t>-2.1982</t>
+  </si>
+  <si>
+    <t>71.7591 + 0.0006*B + 0.0000*C - 0.1554*D - 0.0072*E - 0.0003*F + 0.0000*G - 0.3976*H + 0.0247*I + 0.0375*J - 0.4849*K + 3.0471*L + 0.0002*M</t>
+  </si>
+  <si>
+    <t>71.7591</t>
+  </si>
+  <si>
+    <t>0.0006</t>
+  </si>
+  <si>
+    <t>-0.1554</t>
+  </si>
+  <si>
+    <t>-0.0072</t>
+  </si>
+  <si>
+    <t>-0.3976</t>
+  </si>
+  <si>
+    <t>0.0247</t>
+  </si>
+  <si>
+    <t>0.0375</t>
+  </si>
+  <si>
+    <t>-0.4849</t>
+  </si>
+  <si>
+    <t>3.0471</t>
+  </si>
+  <si>
+    <t>0.0002</t>
+  </si>
+  <si>
+    <t>146.1916 - 0.0036*B + 0.0000*C - 0.0115*D + 0.0095*E - 0.0024*F + 0.0000*G + 0.0416*H + 0.0105*I - 0.0811*J - 0.1580*K - 8.9680*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>146.1916</t>
+  </si>
+  <si>
+    <t>-0.0036</t>
+  </si>
+  <si>
+    <t>-0.0115</t>
+  </si>
+  <si>
+    <t>0.0095</t>
+  </si>
+  <si>
+    <t>0.0416</t>
+  </si>
+  <si>
+    <t>0.0105</t>
+  </si>
+  <si>
+    <t>-0.0811</t>
+  </si>
+  <si>
+    <t>-0.158</t>
+  </si>
+  <si>
+    <t>-8.968</t>
+  </si>
+  <si>
+    <t>-35.1395 - 0.0031*B + 0.0000*C + 0.4136*D - 0.0186*E + 0.0000*F + 0.0000*G - 0.0837*H + 0.0201*I - 0.1264*J + 0.1748*K + 0.2636*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-35.1395</t>
+  </si>
+  <si>
+    <t>0.4136</t>
+  </si>
+  <si>
+    <t>-0.0186</t>
+  </si>
+  <si>
+    <t>-0.0837</t>
+  </si>
+  <si>
+    <t>0.0201</t>
+  </si>
+  <si>
+    <t>-0.1264</t>
+  </si>
+  <si>
+    <t>0.1748</t>
+  </si>
+  <si>
+    <t>0.2636</t>
+  </si>
+  <si>
+    <t>65.7078 - 0.0006*B + 0.0000*C - 0.0348*D - 0.0030*E + 0.0006*F + 0.0000*G - 0.0906*H + 0.0089*I + 0.1427*J - 0.4786*K + 6.7737*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>65.7078</t>
+  </si>
+  <si>
+    <t>-0.0006</t>
+  </si>
+  <si>
+    <t>-0.0348</t>
+  </si>
+  <si>
+    <t>-0.003</t>
+  </si>
+  <si>
+    <t>-0.0906</t>
+  </si>
+  <si>
+    <t>0.0089</t>
+  </si>
+  <si>
+    <t>0.1427</t>
+  </si>
+  <si>
+    <t>-0.4786</t>
+  </si>
+  <si>
+    <t>6.7737</t>
+  </si>
+  <si>
+    <t>-20.9180 + 0.0001*B + 0.0000*C + 0.1422*D - 0.0102*E + 0.0022*F + 0.0000*G - 0.3334*H - 0.0090*I + 0.0771*J - 0.0446*K - 1.8927*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>-20.918</t>
+  </si>
+  <si>
+    <t>0.1422</t>
+  </si>
+  <si>
+    <t>-0.0102</t>
+  </si>
+  <si>
+    <t>0.0022</t>
+  </si>
+  <si>
+    <t>-0.3334</t>
+  </si>
+  <si>
+    <t>-0.009</t>
+  </si>
+  <si>
+    <t>0.0771</t>
+  </si>
+  <si>
+    <t>-0.0446</t>
+  </si>
+  <si>
+    <t>-1.8927</t>
+  </si>
+  <si>
+    <t>43.8634 + 0.0005*B + 0.0000*C + 0.2122*D - 0.0123*E - 0.0011*F + 0.0000*G + 0.1631*H + 0.0082*I - 0.0004*J - 0.1098*K + 4.1505*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>43.8634</t>
+  </si>
+  <si>
+    <t>0.2122</t>
+  </si>
+  <si>
+    <t>-0.0123</t>
+  </si>
+  <si>
+    <t>0.1631</t>
+  </si>
+  <si>
+    <t>0.0082</t>
+  </si>
+  <si>
+    <t>-0.0004</t>
+  </si>
+  <si>
+    <t>-0.1098</t>
+  </si>
+  <si>
+    <t>4.1505</t>
+  </si>
+  <si>
+    <t>77.7013 - 0.0013*B + 0.0000*C + 0.0420*D + 0.0077*E + 0.0117*F + 0.0000*G + 0.1896*H + 0.0181*I + 0.0033*J + 0.0438*K - 0.7193*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>77.7013</t>
+  </si>
+  <si>
+    <t>-0.0013</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>0.0077</t>
+  </si>
+  <si>
+    <t>0.0117</t>
+  </si>
+  <si>
+    <t>0.1896</t>
+  </si>
+  <si>
+    <t>0.0181</t>
+  </si>
+  <si>
+    <t>0.0033</t>
+  </si>
+  <si>
+    <t>0.0438</t>
+  </si>
+  <si>
+    <t>-0.7193</t>
+  </si>
+  <si>
+    <t>-17.8641 - 0.0007*B + 0.0000*C + 0.2053*D - 0.0122*E + 0.0234*F + 0.0000*G - 0.5388*H - 0.0179*I + 0.1046*J + 0.0737*K + 2.1462*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>-17.8641</t>
+  </si>
+  <si>
+    <t>0.2053</t>
+  </si>
+  <si>
+    <t>0.0234</t>
+  </si>
+  <si>
+    <t>-0.5388</t>
+  </si>
+  <si>
+    <t>-0.0179</t>
+  </si>
+  <si>
+    <t>0.1046</t>
+  </si>
+  <si>
+    <t>0.0737</t>
+  </si>
+  <si>
+    <t>2.1462</t>
+  </si>
+  <si>
+    <t>-1.2277 - 0.0025*B + 0.0000*C + 0.1009*D - 0.0107*E + 0.0131*F + 0.0000*G - 0.1949*H - 0.0124*I - 0.0272*J - 0.0294*K - 1.4966*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-1.2277</t>
+  </si>
+  <si>
+    <t>0.1009</t>
+  </si>
+  <si>
+    <t>-0.0107</t>
+  </si>
+  <si>
+    <t>-0.1949</t>
+  </si>
+  <si>
+    <t>-0.0124</t>
+  </si>
+  <si>
+    <t>-0.0272</t>
+  </si>
+  <si>
+    <t>-0.0294</t>
+  </si>
+  <si>
+    <t>-1.4966</t>
+  </si>
+  <si>
+    <t>34.8871 - 0.0005*B + 0.0000*C - 0.0161*D - 0.0086*E + 0.0062*F + 0.0000*G - 0.7157*H - 0.0207*I - 0.0625*J - 0.1999*K + 1.1857*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>34.8871</t>
+  </si>
+  <si>
+    <t>-0.0161</t>
+  </si>
+  <si>
+    <t>-0.7157</t>
+  </si>
+  <si>
+    <t>-0.0207</t>
+  </si>
+  <si>
+    <t>-0.0625</t>
+  </si>
+  <si>
+    <t>-0.1999</t>
+  </si>
+  <si>
+    <t>1.1857</t>
+  </si>
+  <si>
+    <t>121.5247 - 0.0012*B + 0.0000*C + 0.0819*D - 0.0141*E + 0.0039*F + 0.0000*G - 0.2516*H + 0.0041*I - 0.0722*J - 0.0004*K + 4.9327*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>121.5247</t>
+  </si>
+  <si>
+    <t>0.0819</t>
+  </si>
+  <si>
+    <t>-0.0141</t>
+  </si>
+  <si>
+    <t>-0.2516</t>
+  </si>
+  <si>
+    <t>-0.0722</t>
+  </si>
+  <si>
+    <t>4.9327</t>
+  </si>
+  <si>
+    <t>57.1859 + 0.0003*B + 0.0000*C + 0.0051*D - 0.0014*E + 0.0042*F + 0.0000*G - 0.0969*H - 0.0116*I + 0.0036*J - 0.0062*K + 4.6825*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>57.1859</t>
+  </si>
+  <si>
+    <t>0.0003</t>
+  </si>
+  <si>
+    <t>0.0051</t>
+  </si>
+  <si>
+    <t>-0.0014</t>
+  </si>
+  <si>
+    <t>0.0042</t>
+  </si>
+  <si>
+    <t>-0.0969</t>
+  </si>
+  <si>
+    <t>-0.0116</t>
+  </si>
+  <si>
+    <t>0.0036</t>
+  </si>
+  <si>
+    <t>4.6825</t>
+  </si>
+  <si>
+    <t>304.3359 - 0.0023*B + 0.0000*C + 0.2609*D - 0.0018*E + 0.0243*F + 0.0000*G - 0.4596*H - 0.0126*I - 0.0519*J - 0.7198*K - 1.3801*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>304.3359</t>
+  </si>
+  <si>
+    <t>-0.0023</t>
+  </si>
+  <si>
+    <t>0.2609</t>
+  </si>
+  <si>
+    <t>-0.0018</t>
+  </si>
+  <si>
+    <t>-0.4596</t>
+  </si>
+  <si>
+    <t>-0.0126</t>
+  </si>
+  <si>
+    <t>-0.0519</t>
+  </si>
+  <si>
+    <t>-0.7198</t>
+  </si>
+  <si>
+    <t>-1.3801</t>
+  </si>
+  <si>
+    <t>21.7225 - 0.0003*B + 0.0000*C + 0.4626*D + 0.0062*E - 0.0012*F + 0.0000*G - 0.4957*H + 0.0065*I - 0.1161*J + 0.3567*K + 3.8493*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>21.7225</t>
+  </si>
+  <si>
+    <t>0.4626</t>
+  </si>
+  <si>
+    <t>-0.4957</t>
+  </si>
+  <si>
+    <t>0.0065</t>
+  </si>
+  <si>
+    <t>-0.1161</t>
+  </si>
+  <si>
+    <t>0.3567</t>
+  </si>
+  <si>
+    <t>3.8493</t>
+  </si>
+  <si>
+    <t>-241.2400 + 0.0015*B + 0.0000*C + 0.0627*D + 0.0092*E - 0.0106*F + 0.0000*G - 0.3760*H - 0.0005*I + 0.0056*J - 0.2643*K + 2.1423*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-241.24</t>
+  </si>
+  <si>
+    <t>0.0627</t>
+  </si>
+  <si>
+    <t>0.0092</t>
+  </si>
+  <si>
+    <t>-0.0106</t>
+  </si>
+  <si>
+    <t>-0.376</t>
+  </si>
+  <si>
+    <t>0.0056</t>
+  </si>
+  <si>
+    <t>-0.2643</t>
+  </si>
+  <si>
+    <t>2.1423</t>
+  </si>
+  <si>
+    <t>-19.5908 - 0.0007*B + 0.0000*C + 0.1890*D + 0.0037*E - 0.0063*F + 0.0000*G - 0.7502*H + 0.0177*I + 0.0311*J - 0.3455*K + 4.9892*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-19.5908</t>
+  </si>
+  <si>
+    <t>0.189</t>
+  </si>
+  <si>
+    <t>-0.7502</t>
+  </si>
+  <si>
+    <t>0.0177</t>
+  </si>
+  <si>
+    <t>0.0311</t>
+  </si>
+  <si>
+    <t>-0.3455</t>
+  </si>
+  <si>
+    <t>4.9892</t>
+  </si>
+  <si>
+    <t>166.9110 - 0.0008*B + 0.0000*C + 0.4996*D + 0.0145*E + 0.0018*F + 0.0000*G + 0.2529*H + 0.0087*I + 0.1234*J - 0.4044*K + 2.3362*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>166.911</t>
+  </si>
+  <si>
+    <t>0.4996</t>
+  </si>
+  <si>
+    <t>0.0145</t>
+  </si>
+  <si>
+    <t>0.0018</t>
+  </si>
+  <si>
+    <t>0.2529</t>
+  </si>
+  <si>
+    <t>0.0087</t>
+  </si>
+  <si>
+    <t>0.1234</t>
+  </si>
+  <si>
+    <t>-0.4044</t>
+  </si>
+  <si>
+    <t>2.3362</t>
+  </si>
+  <si>
+    <t>-247.6753 - 0.0030*B + 0.0000*C - 0.3239*D - 0.0065*E + 0.0107*F + 0.0000*G + 0.4654*H + 0.0005*I + 0.1465*J - 0.5174*K - 4.9916*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-247.6753</t>
+  </si>
+  <si>
+    <t>-0.3239</t>
+  </si>
+  <si>
+    <t>0.0107</t>
+  </si>
+  <si>
+    <t>0.4654</t>
+  </si>
+  <si>
+    <t>0.1465</t>
+  </si>
+  <si>
+    <t>-0.5174</t>
+  </si>
+  <si>
+    <t>-4.9916</t>
+  </si>
+  <si>
+    <t>54.6959 - 0.0010*B + 0.0000*C - 0.3295*D - 0.0046*E - 0.0079*F + 0.0000*G + 0.1320*H + 0.0047*I - 0.0823*J - 0.2816*K - 3.0161*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>54.6959</t>
+  </si>
+  <si>
+    <t>-0.3295</t>
+  </si>
+  <si>
+    <t>-0.0046</t>
+  </si>
+  <si>
+    <t>-0.0079</t>
+  </si>
+  <si>
+    <t>0.132</t>
+  </si>
+  <si>
+    <t>0.0047</t>
+  </si>
+  <si>
+    <t>-0.0823</t>
+  </si>
+  <si>
+    <t>-0.2816</t>
+  </si>
+  <si>
+    <t>-3.0161</t>
+  </si>
+  <si>
+    <t>135.2805 - 0.0026*B + 0.0000*C + 0.1870*D - 0.0092*E - 0.0032*F + 0.0000*G - 0.1789*H - 0.0154*I - 0.0479*J - 0.4678*K + 6.2575*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>135.2805</t>
+  </si>
+  <si>
+    <t>-0.0026</t>
+  </si>
+  <si>
+    <t>0.187</t>
+  </si>
+  <si>
+    <t>-0.0092</t>
+  </si>
+  <si>
+    <t>-0.1789</t>
+  </si>
+  <si>
+    <t>-0.0154</t>
+  </si>
+  <si>
+    <t>-0.0479</t>
+  </si>
+  <si>
+    <t>-0.4678</t>
+  </si>
+  <si>
+    <t>6.2575</t>
+  </si>
+  <si>
+    <t>-98.2379 - 0.0005*B + 0.0000*C + 0.0632*D - 0.0060*E + 0.0098*F + 0.0000*G + 0.1672*H - 0.0081*I - 0.0498*J - 0.2166*K - 6.8271*L - 0.0001*M</t>
+  </si>
+  <si>
+    <t>-98.2379</t>
+  </si>
+  <si>
+    <t>0.0632</t>
+  </si>
+  <si>
+    <t>0.0098</t>
+  </si>
+  <si>
+    <t>0.1672</t>
+  </si>
+  <si>
+    <t>-0.0498</t>
+  </si>
+  <si>
+    <t>-0.2166</t>
+  </si>
+  <si>
+    <t>-6.8271</t>
+  </si>
+  <si>
+    <t>193.3800 + 0.0020*B + 0.0000*C + 0.0357*D + 0.0023*E + 0.0070*F + 0.0000*G + 1.0649*H + 0.0155*I - 0.0099*J - 0.4018*K - 4.6943*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>193.38</t>
+  </si>
+  <si>
+    <t>0.002</t>
+  </si>
+  <si>
+    <t>0.0357</t>
+  </si>
+  <si>
+    <t>0.007</t>
+  </si>
+  <si>
+    <t>1.0649</t>
+  </si>
+  <si>
+    <t>0.0155</t>
+  </si>
+  <si>
+    <t>-0.0099</t>
+  </si>
+  <si>
+    <t>-0.4018</t>
+  </si>
+  <si>
+    <t>-4.6943</t>
+  </si>
+  <si>
+    <t>-106.2282 - 0.0034*B + 0.0000*C - 0.0441*D - 0.0149*E + 0.0196*F + 0.0000*G + 0.2169*H - 0.0007*I + 0.1333*J - 0.1207*K - 2.4091*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>-106.2282</t>
+  </si>
+  <si>
+    <t>-0.0441</t>
+  </si>
+  <si>
+    <t>-0.0149</t>
+  </si>
+  <si>
+    <t>0.0196</t>
+  </si>
+  <si>
+    <t>0.2169</t>
+  </si>
+  <si>
+    <t>0.1333</t>
+  </si>
+  <si>
+    <t>-0.1207</t>
+  </si>
+  <si>
+    <t>-2.4091</t>
+  </si>
+  <si>
+    <t>76.5460 - 0.0027*B + 0.0000*C + 0.0475*D - 0.0128*E - 0.0086*F + 0.0000*G + 0.2347*H + 0.0268*I - 0.1231*J + 0.0114*K - 1.7631*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>76.546</t>
+  </si>
+  <si>
+    <t>-0.0027</t>
+  </si>
+  <si>
+    <t>0.0475</t>
+  </si>
+  <si>
+    <t>-0.0128</t>
+  </si>
+  <si>
+    <t>0.2347</t>
+  </si>
+  <si>
+    <t>0.0268</t>
+  </si>
+  <si>
+    <t>-0.1231</t>
+  </si>
+  <si>
+    <t>0.0114</t>
+  </si>
+  <si>
+    <t>-1.7631</t>
+  </si>
+  <si>
+    <t>-83.0923 - 0.0024*B + 0.0000*C + 0.0955*D - 0.0123*E + 0.0066*F + 0.0000*G - 0.1562*H - 0.0040*I - 0.0794*J - 0.2987*K + 2.5488*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>-83.0923</t>
+  </si>
+  <si>
+    <t>0.0955</t>
+  </si>
+  <si>
+    <t>0.0066</t>
+  </si>
+  <si>
+    <t>-0.1562</t>
+  </si>
+  <si>
+    <t>-0.004</t>
+  </si>
+  <si>
+    <t>-0.2987</t>
+  </si>
+  <si>
+    <t>2.5488</t>
+  </si>
+  <si>
+    <t>-137.4424 - 0.0007*B + 0.0000*C + 0.2366*D - 0.0210*E + 0.0091*F + 0.0000*G - 0.4013*H + 0.0076*I - 0.0665*J - 0.6330*K - 4.7590*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-137.4424</t>
+  </si>
+  <si>
+    <t>0.2366</t>
+  </si>
+  <si>
+    <t>-0.021</t>
+  </si>
+  <si>
+    <t>0.0091</t>
+  </si>
+  <si>
+    <t>-0.4013</t>
+  </si>
+  <si>
+    <t>0.0076</t>
+  </si>
+  <si>
+    <t>-0.0665</t>
+  </si>
+  <si>
+    <t>-0.633</t>
+  </si>
+  <si>
+    <t>-4.759</t>
+  </si>
+  <si>
+    <t>37.1498 - 0.0025*B + 0.0000*C + 0.2140*D - 0.0210*E + 0.0035*F + 0.0000*G - 0.6208*H - 0.0099*I + 0.0057*J - 0.3759*K - 0.9471*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>37.1498</t>
+  </si>
+  <si>
+    <t>0.214</t>
+  </si>
+  <si>
+    <t>0.0035</t>
+  </si>
+  <si>
+    <t>-0.6208</t>
+  </si>
+  <si>
+    <t>0.0057</t>
+  </si>
+  <si>
+    <t>-0.3759</t>
+  </si>
+  <si>
+    <t>-0.9471</t>
+  </si>
+  <si>
+    <t>-80.9048 + 0.0006*B + 0.0000*C - 0.1412*D + 0.0018*E + 0.0174*F + 0.0000*G - 1.1255*H - 0.0119*I + 0.0529*J - 0.1970*K + 1.3704*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-80.9048</t>
+  </si>
+  <si>
+    <t>-0.1412</t>
+  </si>
+  <si>
+    <t>0.0174</t>
+  </si>
+  <si>
+    <t>-1.1255</t>
+  </si>
+  <si>
+    <t>-0.0119</t>
+  </si>
+  <si>
+    <t>0.0529</t>
+  </si>
+  <si>
+    <t>-0.197</t>
+  </si>
+  <si>
+    <t>1.3704</t>
+  </si>
+  <si>
+    <t>12.7191 - 0.0012*B + 0.0000*C + 0.3203*D - 0.0011*E + 0.0072*F + 0.0000*G - 0.3009*H - 0.0075*I - 0.0371*J - 0.0344*K - 1.0588*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>12.7191</t>
+  </si>
+  <si>
+    <t>0.3203</t>
+  </si>
+  <si>
+    <t>0.0072</t>
+  </si>
+  <si>
+    <t>-0.3009</t>
+  </si>
+  <si>
+    <t>-0.0075</t>
+  </si>
+  <si>
+    <t>-0.0371</t>
+  </si>
+  <si>
+    <t>-0.0344</t>
+  </si>
+  <si>
+    <t>-1.0588</t>
+  </si>
+  <si>
+    <t>293.3602 + 0.0006*B + 0.0000*C + 0.0202*D + 0.0088*E + 0.0003*F + 0.0000*G - 0.9519*H - 0.0150*I - 0.1652*J - 0.2374*K + 0.2887*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>293.3602</t>
+  </si>
+  <si>
+    <t>0.0202</t>
+  </si>
+  <si>
+    <t>0.0088</t>
+  </si>
+  <si>
+    <t>-0.9519</t>
+  </si>
+  <si>
+    <t>-0.015</t>
+  </si>
+  <si>
+    <t>-0.1652</t>
+  </si>
+  <si>
+    <t>-0.2374</t>
+  </si>
+  <si>
+    <t>0.2887</t>
+  </si>
+  <si>
+    <t>46.6331 - 0.0013*B + 0.0000*C + 0.2523*D - 0.0267*E + 0.0063*F + 0.0000*G + 0.1725*H - 0.0217*I + 0.1033*J - 0.0496*K - 1.0413*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>46.6331</t>
+  </si>
+  <si>
+    <t>0.2523</t>
+  </si>
+  <si>
+    <t>-0.0267</t>
+  </si>
+  <si>
+    <t>0.0063</t>
+  </si>
+  <si>
+    <t>0.1725</t>
+  </si>
+  <si>
+    <t>-0.0217</t>
+  </si>
+  <si>
+    <t>0.1033</t>
+  </si>
+  <si>
+    <t>-0.0496</t>
+  </si>
+  <si>
+    <t>-1.0413</t>
+  </si>
+  <si>
+    <t>320.9178 - 0.0006*B + 0.0000*C + 0.1356*D - 0.0085*E - 0.0037*F + 0.0000*G + 0.1964*H - 0.0128*I + 0.0078*J - 0.2718*K + 1.7011*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>320.9178</t>
+  </si>
+  <si>
+    <t>0.1356</t>
+  </si>
+  <si>
+    <t>-0.0085</t>
+  </si>
+  <si>
+    <t>-0.0037</t>
+  </si>
+  <si>
+    <t>0.1964</t>
+  </si>
+  <si>
+    <t>0.0078</t>
+  </si>
+  <si>
+    <t>-0.2718</t>
+  </si>
+  <si>
+    <t>1.7011</t>
+  </si>
+  <si>
+    <t>146.9076 - 0.0018*B + 0.0000*C + 0.0315*D - 0.0139*E + 0.0000*F + 0.0000*G + 0.0150*H + 0.0103*I - 0.0807*J + 0.0949*K + 4.3896*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>146.9076</t>
+  </si>
+  <si>
+    <t>0.0315</t>
+  </si>
+  <si>
+    <t>0.015</t>
+  </si>
+  <si>
+    <t>-0.0807</t>
+  </si>
+  <si>
+    <t>0.0949</t>
+  </si>
+  <si>
+    <t>4.3896</t>
+  </si>
+  <si>
+    <t>265.3350 - 0.0023*B + 0.0000*C - 0.1643*D - 0.0222*E + 0.0179*F + 0.0000*G + 0.1259*H - 0.0013*I + 0.0264*J - 0.4481*K + 7.7327*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>265.335</t>
+  </si>
+  <si>
+    <t>-0.1643</t>
+  </si>
+  <si>
+    <t>-0.0222</t>
+  </si>
+  <si>
+    <t>0.0179</t>
+  </si>
+  <si>
+    <t>0.1259</t>
+  </si>
+  <si>
+    <t>0.0264</t>
+  </si>
+  <si>
+    <t>-0.4481</t>
+  </si>
+  <si>
+    <t>7.7327</t>
+  </si>
+  <si>
+    <t>15.9371 + 0.0004*B + 0.0000*C + 0.1823*D - 0.0014*E - 0.0032*F + 0.0000*G + 0.0527*H + 0.0264*I + 0.1213*J + 0.2918*K - 1.3355*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>15.9371</t>
+  </si>
+  <si>
+    <t>0.1823</t>
+  </si>
+  <si>
+    <t>0.0527</t>
+  </si>
+  <si>
+    <t>0.1213</t>
+  </si>
+  <si>
+    <t>0.2918</t>
+  </si>
+  <si>
+    <t>-1.3355</t>
+  </si>
+  <si>
+    <t>-17.2494 - 0.0008*B + 0.0000*C + 0.3055*D - 0.0213*E + 0.0182*F + 0.0000*G - 0.1993*H - 0.0067*I - 0.0887*J - 0.5922*K + 2.7567*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-17.2494</t>
+  </si>
+  <si>
+    <t>0.3055</t>
+  </si>
+  <si>
+    <t>-0.0213</t>
+  </si>
+  <si>
+    <t>0.0182</t>
+  </si>
+  <si>
+    <t>-0.1993</t>
+  </si>
+  <si>
+    <t>-0.0067</t>
+  </si>
+  <si>
+    <t>-0.0887</t>
+  </si>
+  <si>
+    <t>-0.5922</t>
+  </si>
+  <si>
+    <t>2.7567</t>
+  </si>
+  <si>
+    <t>-181.5260 - 0.0032*B + 0.0000*C + 0.0183*D + 0.0136*E + 0.0017*F + 0.0000*G - 0.7378*H - 0.0041*I - 0.0228*J - 0.8757*K + 0.0657*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-181.526</t>
+  </si>
+  <si>
+    <t>0.0183</t>
+  </si>
+  <si>
+    <t>0.0136</t>
+  </si>
+  <si>
+    <t>0.0017</t>
+  </si>
+  <si>
+    <t>-0.7378</t>
+  </si>
+  <si>
+    <t>-0.0041</t>
+  </si>
+  <si>
+    <t>-0.0228</t>
+  </si>
+  <si>
+    <t>-0.8757</t>
+  </si>
+  <si>
+    <t>0.0657</t>
+  </si>
+  <si>
+    <t>98.7421 + 0.0023*B + 0.0000*C + 0.3120*D - 0.0065*E - 0.0061*F + 0.0000*G + 0.8941*H + 0.0003*I + 0.0027*J - 0.1483*K + 0.8397*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>98.7421</t>
+  </si>
+  <si>
+    <t>0.312</t>
+  </si>
+  <si>
+    <t>-0.0061</t>
+  </si>
+  <si>
+    <t>0.8941</t>
+  </si>
+  <si>
+    <t>0.0027</t>
+  </si>
+  <si>
+    <t>-0.1483</t>
+  </si>
+  <si>
+    <t>0.8397</t>
+  </si>
+  <si>
+    <t>-80.4490 - 0.0019*B + 0.0000*C + 0.0791*D - 0.0093*E - 0.0025*F + 0.0000*G - 0.0934*H - 0.0042*I + 0.1354*J - 0.8633*K + 3.5796*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>-80.449</t>
+  </si>
+  <si>
+    <t>-0.0019</t>
+  </si>
+  <si>
+    <t>0.0791</t>
+  </si>
+  <si>
+    <t>-0.0093</t>
+  </si>
+  <si>
+    <t>-0.0934</t>
+  </si>
+  <si>
+    <t>0.1354</t>
+  </si>
+  <si>
+    <t>-0.8633</t>
+  </si>
+  <si>
+    <t>3.5796</t>
+  </si>
+  <si>
+    <t>-292.0757 - 0.0015*B + 0.0000*C + 0.0111*D - 0.0183*E - 0.0031*F + 0.0000*G - 0.5806*H + 0.0245*I + 0.0848*J + 0.2043*K + 2.4454*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-292.0757</t>
+  </si>
+  <si>
+    <t>-0.0183</t>
+  </si>
+  <si>
+    <t>-0.5806</t>
+  </si>
+  <si>
+    <t>0.0245</t>
+  </si>
+  <si>
+    <t>0.0848</t>
+  </si>
+  <si>
+    <t>0.2043</t>
+  </si>
+  <si>
+    <t>2.4454</t>
+  </si>
+  <si>
+    <t>-73.5146 - 0.0001*B + 0.0000*C - 0.1598*D + 0.0037*E + 0.0019*F + 0.0000*G - 0.2861*H + 0.0096*I + 0.0410*J - 0.2400*K + 3.7876*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-73.5146</t>
+  </si>
+  <si>
+    <t>-0.1598</t>
+  </si>
+  <si>
+    <t>-0.2861</t>
+  </si>
+  <si>
+    <t>0.0096</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>-0.24</t>
+  </si>
+  <si>
+    <t>3.7876</t>
+  </si>
+  <si>
+    <t>87.4151 + 0.0001*B + 0.0000*C + 0.0235*D - 0.0003*E - 0.0074*F + 0.0000*G + 0.2339*H - 0.0032*I - 0.0451*J + 0.1437*K - 1.9278*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>87.4151</t>
+  </si>
+  <si>
+    <t>0.0235</t>
+  </si>
+  <si>
+    <t>-0.0074</t>
+  </si>
+  <si>
+    <t>0.2339</t>
+  </si>
+  <si>
+    <t>-0.0451</t>
+  </si>
+  <si>
+    <t>0.1437</t>
+  </si>
+  <si>
+    <t>-1.9278</t>
+  </si>
+  <si>
+    <t>-219.1555 + 0.0001*B + 0.0000*C - 0.1715*D + 0.0145*E - 0.0151*F + 0.0000*G + 0.5431*H + 0.0025*I - 0.0072*J - 0.2901*K + 1.4563*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-219.1555</t>
+  </si>
+  <si>
+    <t>-0.1715</t>
+  </si>
+  <si>
+    <t>-0.0151</t>
+  </si>
+  <si>
+    <t>0.5431</t>
+  </si>
+  <si>
+    <t>0.0025</t>
+  </si>
+  <si>
+    <t>-0.2901</t>
+  </si>
+  <si>
+    <t>1.4563</t>
+  </si>
+  <si>
+    <t>156.1873 - 0.0007*B + 0.0000*C + 0.1159*D - 0.0075*E + 0.0036*F + 0.0000*G - 0.0128*H - 0.0250*I - 0.1186*J + 0.0605*K + 0.7562*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>156.1873</t>
+  </si>
+  <si>
+    <t>0.1159</t>
+  </si>
+  <si>
+    <t>-0.025</t>
+  </si>
+  <si>
+    <t>-0.1186</t>
+  </si>
+  <si>
+    <t>0.0605</t>
+  </si>
+  <si>
+    <t>0.7562</t>
+  </si>
+  <si>
+    <t>3.1016 - 0.0003*B + 0.0000*C - 0.0227*D - 0.0118*E + 0.0059*F + 0.0000*G - 0.5277*H + 0.0053*I - 0.1502*J + 0.1383*K + 1.6816*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>3.1016</t>
+  </si>
+  <si>
+    <t>-0.0227</t>
+  </si>
+  <si>
+    <t>-0.0118</t>
+  </si>
+  <si>
+    <t>0.0059</t>
+  </si>
+  <si>
+    <t>-0.5277</t>
+  </si>
+  <si>
+    <t>0.0053</t>
+  </si>
+  <si>
+    <t>-0.1502</t>
+  </si>
+  <si>
+    <t>0.1383</t>
+  </si>
+  <si>
+    <t>1.6816</t>
+  </si>
+  <si>
+    <t>139.1679 + 0.0020*B + 0.0000*C + 0.2895*D - 0.0228*E - 0.0077*F + 0.0000*G - 0.3862*H - 0.0002*I + 0.0476*J - 0.3393*K + 0.8050*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>139.1679</t>
+  </si>
+  <si>
+    <t>0.2895</t>
+  </si>
+  <si>
+    <t>-0.0077</t>
+  </si>
+  <si>
+    <t>-0.3862</t>
+  </si>
+  <si>
+    <t>0.0476</t>
+  </si>
+  <si>
+    <t>-0.3393</t>
+  </si>
+  <si>
+    <t>0.805</t>
+  </si>
+  <si>
+    <t>-85.7909 - 0.0034*B + 0.0000*C - 0.0997*D - 0.0177*E - 0.0049*F + 0.0000*G + 0.2858*H - 0.0141*I + 0.2359*J - 0.0075*K + 0.7991*L + -0.0000*M</t>
+  </si>
+  <si>
+    <t>-85.7909</t>
+  </si>
+  <si>
+    <t>-0.0997</t>
+  </si>
+  <si>
+    <t>-0.0177</t>
+  </si>
+  <si>
+    <t>-0.0049</t>
+  </si>
+  <si>
+    <t>0.2359</t>
+  </si>
+  <si>
+    <t>0.7991</t>
+  </si>
+  <si>
+    <t>99.3211 - 0.0019*B + 0.0000*C + 0.1102*D + 0.0229*E + 0.0032*F + 0.0000*G + 0.3240*H - 0.0106*I - 0.0017*J + 0.3402*K - 1.6905*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>99.3211</t>
+  </si>
+  <si>
+    <t>0.1102</t>
+  </si>
+  <si>
+    <t>0.0229</t>
+  </si>
+  <si>
+    <t>0.0032</t>
+  </si>
+  <si>
+    <t>0.324</t>
+  </si>
+  <si>
+    <t>-0.0017</t>
+  </si>
+  <si>
+    <t>0.3402</t>
+  </si>
+  <si>
+    <t>-1.6905</t>
+  </si>
+  <si>
+    <t>100.3713 - 0.0019*B + 0.0000*C + 0.2127*D + 0.0064*E + 0.0098*F + 0.0000*G - 0.7646*H - 0.0109*I - 0.0206*J - 0.1620*K + 2.1357*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>100.3713</t>
+  </si>
+  <si>
+    <t>0.2127</t>
+  </si>
+  <si>
+    <t>-0.7646</t>
+  </si>
+  <si>
+    <t>-0.0109</t>
+  </si>
+  <si>
+    <t>-0.0206</t>
+  </si>
+  <si>
+    <t>-0.162</t>
+  </si>
+  <si>
+    <t>2.1357</t>
+  </si>
+  <si>
+    <t>-187.9300 - 0.0002*B + 0.0000*C + 0.2084*D + 0.0021*E + 0.0141*F + 0.0000*G + 0.1978*H + 0.0060*I - 0.0048*J - 0.5938*K + 1.5498*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-187.93</t>
+  </si>
+  <si>
+    <t>0.2084</t>
+  </si>
+  <si>
+    <t>0.1978</t>
+  </si>
+  <si>
+    <t>0.006</t>
+  </si>
+  <si>
+    <t>-0.0048</t>
+  </si>
+  <si>
+    <t>-0.5938</t>
+  </si>
+  <si>
+    <t>1.5498</t>
+  </si>
+  <si>
+    <t>38.8229 - 0.0031*B + 0.0000*C - 0.1314*D + 0.0072*E + 0.0037*F + 0.0000*G + 0.1368*H - 0.0001*I + 0.0041*J + 0.1136*K - 1.3503*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>38.8229</t>
+  </si>
+  <si>
+    <t>-0.1314</t>
+  </si>
+  <si>
+    <t>0.1368</t>
+  </si>
+  <si>
+    <t>0.1136</t>
+  </si>
+  <si>
+    <t>-1.3503</t>
+  </si>
+  <si>
+    <t>-64.7313 - 0.0017*B + 0.0000*C + 0.0236*D - 0.0014*E - 0.0003*F + 0.0000*G + 0.3667*H - 0.0133*I - 0.0152*J - 0.2614*K + 4.6697*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>-64.7313</t>
+  </si>
+  <si>
+    <t>0.3667</t>
+  </si>
+  <si>
+    <t>-0.0133</t>
+  </si>
+  <si>
+    <t>-0.0152</t>
+  </si>
+  <si>
+    <t>-0.2614</t>
+  </si>
+  <si>
+    <t>4.6697</t>
+  </si>
+  <si>
+    <t>146.1040 - 0.0035*B + 0.0000*C + 0.1394*D + 0.0055*E + 0.0049*F + 0.0000*G + 0.2905*H - 0.0079*I + 0.1270*J + 0.4839*K - 0.8805*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>146.104</t>
+  </si>
+  <si>
+    <t>-0.0035</t>
+  </si>
+  <si>
+    <t>0.1394</t>
+  </si>
+  <si>
+    <t>0.0055</t>
+  </si>
+  <si>
+    <t>0.0049</t>
+  </si>
+  <si>
+    <t>0.2905</t>
+  </si>
+  <si>
+    <t>0.127</t>
+  </si>
+  <si>
+    <t>0.4839</t>
+  </si>
+  <si>
+    <t>-0.8805</t>
+  </si>
+  <si>
+    <t>205.5875 + 0.0019*B + 0.0000*C - 0.0193*D - 0.0081*E + 0.0015*F + 0.0000*G - 0.6743*H - 0.0137*I - 0.0880*J - 0.3507*K + 0.1259*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>205.5875</t>
+  </si>
+  <si>
+    <t>-0.0193</t>
+  </si>
+  <si>
+    <t>-0.6743</t>
+  </si>
+  <si>
+    <t>-0.0137</t>
+  </si>
+  <si>
+    <t>-0.088</t>
+  </si>
+  <si>
+    <t>-0.3507</t>
+  </si>
+  <si>
+    <t>219.2915 - 0.0027*B + 0.0000*C + 0.2834*D - 0.0059*E + 0.0036*F + 0.0000*G + 0.1341*H - 0.0166*I + 0.0355*J - 0.0965*K + 1.7424*L + 0.0000*M</t>
+  </si>
+  <si>
+    <t>219.2915</t>
+  </si>
+  <si>
+    <t>0.2834</t>
+  </si>
+  <si>
+    <t>-0.0059</t>
+  </si>
+  <si>
+    <t>0.1341</t>
+  </si>
+  <si>
+    <t>0.0355</t>
+  </si>
+  <si>
+    <t>-0.0965</t>
+  </si>
+  <si>
+    <t>1.7424</t>
+  </si>
+  <si>
+    <t>346.9678 - 0.0020*B + 0.0000*C - 0.0209*D - 0.0102*E - 0.0010*F + 0.0000*G - 0.3912*H + 0.0165*I + 0.1280*J - 0.2971*K - 2.3204*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>346.9678</t>
+  </si>
+  <si>
+    <t>-0.002</t>
+  </si>
+  <si>
+    <t>-0.0209</t>
+  </si>
+  <si>
+    <t>-0.3912</t>
+  </si>
+  <si>
+    <t>0.0165</t>
+  </si>
+  <si>
+    <t>0.128</t>
+  </si>
+  <si>
+    <t>-0.2971</t>
+  </si>
+  <si>
+    <t>-2.3204</t>
+  </si>
+  <si>
+    <t>-77.4238 + 0.0002*B + 0.0000*C + 0.1265*D - 0.0195*E + 0.0183*F + 0.0000*G + 0.5829*H - 0.0093*I - 0.0331*J - 0.0640*K + 1.2579*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>-77.4238</t>
+  </si>
+  <si>
+    <t>0.1265</t>
+  </si>
+  <si>
+    <t>-0.0195</t>
+  </si>
+  <si>
+    <t>0.5829</t>
+  </si>
+  <si>
+    <t>-0.0331</t>
+  </si>
+  <si>
+    <t>-0.064</t>
+  </si>
+  <si>
+    <t>1.2579</t>
+  </si>
+  <si>
+    <t>284.1603 - 0.0012*B + 0.0000*C - 0.0746*D - 0.0180*E - 0.0026*F + 0.0000*G - 0.1493*H + 0.0251*I - 0.0446*J - 0.0809*K + 0.1819*L + 0.0001*M</t>
+  </si>
+  <si>
+    <t>284.1603</t>
+  </si>
+  <si>
+    <t>-0.0746</t>
+  </si>
+  <si>
+    <t>-0.018</t>
+  </si>
+  <si>
+    <t>-0.1493</t>
+  </si>
+  <si>
+    <t>0.0251</t>
+  </si>
+  <si>
+    <t>-0.0809</t>
+  </si>
+  <si>
+    <t>0.1819</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1336,6 +3548,10 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1355,17 +3571,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="text_format" xfId="2" xr:uid="{4E82491A-5A29-4FB7-9FA0-7DD12EBD30A2}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{18DB56FD-60F1-4B96-A73E-6CF40F365264}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1667,7 +3892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="1" max="15" width="9.23046875" style="2"/>
@@ -3600,8 +5825,3768 @@
         <v>101</v>
       </c>
     </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="O48" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="O50" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="O51" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="I53" s="2">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="O53" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="I55" s="2">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="O55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="I57" s="2">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="I59" s="2">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="O59" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="I60" s="2">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="O60" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="I61" s="2">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="O61" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="E62" s="2">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="I62" s="2">
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="O62" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="E63" s="2">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="I63" s="2">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="M63" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="N63" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="O63" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="N64" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="I65" s="2">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="M65" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="N65" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="O65" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="N66" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="O66" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="N67" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="O67" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="M68" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="N68" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="O68" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="I69" s="2">
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="N69" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="O69" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="M70" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="N70" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="O70" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" s="2">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="N71" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="O71" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="I72" s="2">
+        <v>0</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="O72" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="I73" s="2">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="N73" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="O73" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E74" s="2">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="L74" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="M74" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="N74" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="O74" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" s="2">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="M75" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="N75" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="O75" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="I76" s="2">
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="M76" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="N76" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="O76" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="2">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E77" s="2">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="I77" s="2">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="O77" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="E78" s="2">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="I78" s="2">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="M78" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="O78" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="2">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="I79" s="2">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="M79" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="O79" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="I80" s="2">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="M80" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="N80" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="O80" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" s="2">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="E81" s="2">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="I81" s="2">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="N81" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="O81" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="E82" s="2">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="I82" s="2">
+        <v>0</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="M82" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="N82" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="O82" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" s="2">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="E83" s="2">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="I83" s="2">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="M83" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="N83" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="O83" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="I84" s="2">
+        <v>0</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="M84" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="N84" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="O84" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" s="2">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="E85" s="2">
+        <v>0</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="I85" s="2">
+        <v>0</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="M85" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="N85" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="O85" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="I86" s="2">
+        <v>0</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="M86" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="N86" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="O86" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87" s="2">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="E87" s="2">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="I87" s="2">
+        <v>0</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="N87" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="O87" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="I88" s="2">
+        <v>0</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="M88" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="N88" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="O88" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89" s="2">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="I89" s="2">
+        <v>0</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="M89" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="N89" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="O89" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="I90" s="2">
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="L90" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="M90" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="N90" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="O90" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" s="2">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="I91" s="2">
+        <v>0</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="L91" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="M91" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="N91" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="O91" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="I92" s="2">
+        <v>0</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="M92" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="N92" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="O92" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" s="2">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="I93" s="2">
+        <v>0</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="N93" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="O93" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="I94" s="2">
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="L94" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="M94" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="N94" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="O94" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95" s="2">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="I95" s="2">
+        <v>0</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="L95" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="M95" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="N95" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="O95" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="I96" s="2">
+        <v>0</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="L96" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="M96" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="N96" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="O96" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97" s="2">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="I97" s="2">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="M97" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="N97" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="O97" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="I98" s="2">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="M98" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="N98" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="O98" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99" s="2">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="I99" s="2">
+        <v>0</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="L99" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="M99" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="N99" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="O99" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="E100" s="2">
+        <v>0</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="I100" s="2">
+        <v>0</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="L100" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="M100" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="N100" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="O100" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101" s="2">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E101" s="2">
+        <v>0</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="I101" s="2">
+        <v>0</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="L101" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="M101" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="N101" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="O101" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102" s="2">
+        <v>101</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="I102" s="2">
+        <v>0</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="L102" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="M102" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="N102" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="O102" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103" s="2">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="E103" s="2">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="I103" s="2">
+        <v>0</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="M103" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="N103" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="O103" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104" s="2">
+        <v>103</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="I104" s="2">
+        <v>0</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="L104" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="M104" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="N104" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="O104" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105" s="2">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="I105" s="2">
+        <v>0</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="L105" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="M105" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="N105" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="O105" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106" s="2">
+        <v>105</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="I106" s="2">
+        <v>0</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="K106" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="L106" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="M106" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="N106" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="O106" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107" s="2">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="I107" s="2">
+        <v>0</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="L107" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="M107" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="N107" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="O107" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108" s="2">
+        <v>107</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E108" s="2">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="I108" s="2">
+        <v>0</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="K108" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="L108" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="M108" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="N108" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="O108" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109" s="2">
+        <v>108</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="E109" s="2">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="I109" s="2">
+        <v>0</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="L109" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="M109" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="N109" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="O109" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110" s="2">
+        <v>109</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E110" s="2">
+        <v>0</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I110" s="2">
+        <v>0</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="L110" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="M110" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="N110" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="O110" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111" s="2">
+        <v>110</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="E111" s="2">
+        <v>0</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="I111" s="2">
+        <v>0</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="K111" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="L111" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="M111" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="N111" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="O111" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112" s="2">
+        <v>111</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="E112" s="2">
+        <v>0</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="I112" s="2">
+        <v>0</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="K112" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="L112" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="M112" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="N112" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="O112" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113" s="2">
+        <v>112</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="E113" s="2">
+        <v>0</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="I113" s="2">
+        <v>0</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K113" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="L113" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="M113" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N113" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="O113" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" s="2">
+        <v>113</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="E114" s="2">
+        <v>0</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="I114" s="2">
+        <v>0</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K114" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="L114" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="M114" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="N114" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="O114" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115" s="2">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="E115" s="2">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="I115" s="2">
+        <v>0</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="K115" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="L115" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="M115" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="N115" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="O115" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116" s="2">
+        <v>115</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E116" s="2">
+        <v>0</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I116" s="2">
+        <v>0</v>
+      </c>
+      <c r="J116" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K116" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="L116" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="M116" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="N116" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="O116" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117" s="2">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="E117" s="2">
+        <v>0</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="I117" s="2">
+        <v>0</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L117" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M117" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="N117" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="O117" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118" s="2">
+        <v>117</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="E118" s="2">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="I118" s="2">
+        <v>0</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K118" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="L118" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="M118" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="N118" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="O118" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119" s="2">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="I119" s="2">
+        <v>0</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K119" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L119" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="M119" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="N119" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="O119" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120" s="2">
+        <v>119</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E120" s="2">
+        <v>0</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="I120" s="2">
+        <v>0</v>
+      </c>
+      <c r="J120" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="K120" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="L120" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M120" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="N120" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="O120" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121" s="2">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E121" s="2">
+        <v>0</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="I121" s="2">
+        <v>0</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K121" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="L121" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="M121" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="N121" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="O121" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>